--- a/backend/data/attachments/crawler/Takraf_RDK250.xlsx
+++ b/backend/data/attachments/crawler/Takraf_RDK250.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\crane_lifting_capacity\data\crawler\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F78FE42-3BE4-40BB-BE4A-14D0EC0C6E7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33692EDE-365D-457B-B9EA-F3BD76B6F32F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4290" yWindow="4290" windowWidth="28800" windowHeight="15315" xr2:uid="{D0CD5142-251E-41F7-B82A-77810B023ACC}"/>
+    <workbookView xWindow="5025" yWindow="3225" windowWidth="30900" windowHeight="15660" xr2:uid="{D0CD5142-251E-41F7-B82A-77810B023ACC}"/>
   </bookViews>
   <sheets>
     <sheet name="List1" sheetId="26" r:id="rId1"/>
@@ -48,9 +48,6 @@
     <t>6..6</t>
   </si>
   <si>
-    <t>crawler</t>
-  </si>
-  <si>
     <t>РДК250</t>
   </si>
   <si>
@@ -88,6 +85,9 @@
   </si>
   <si>
     <t>Максимальная грузоподъемность</t>
+  </si>
+  <si>
+    <t>Гусеничный</t>
   </si>
 </sst>
 </file>
@@ -801,21 +801,21 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D1" s="23" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D2" s="23">
         <v>1703.3</v>
@@ -823,21 +823,21 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D3" s="23" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>13</v>
       </c>
       <c r="D4" s="23">
         <v>451.93</v>
@@ -845,13 +845,13 @@
     </row>
     <row r="5" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="D5" s="23" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G5" s="24">
         <v>25</v>
@@ -859,7 +859,7 @@
     </row>
     <row r="6" spans="1:12" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="28" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6" s="29"/>
       <c r="D6" s="29"/>
